--- a/shell_sort/shell_sort_speed_tests/info_grafs.xlsx
+++ b/shell_sort/shell_sort_speed_tests/info_grafs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\programming\nsu\OPK_2\shell_sort\shell_sort_speed_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113AC97E-9AC0-4443-AA8E-5FB6402A0DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF789A86-83A2-4B2E-B396-074AD7273E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,6 +191,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>SELL</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -285,6 +288,9 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>HIBBARD</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -380,12 +386,15 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:v>SEDJVIK</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:prstDash val="sysDot"/>
+              <a:prstDash val="lgDashDotDot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -475,6 +484,9 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:tx>
+            <c:v>GEOMETRIC</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>

--- a/shell_sort/shell_sort_speed_tests/info_grafs.xlsx
+++ b/shell_sort/shell_sort_speed_tests/info_grafs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\programming\nsu\OPK_2\shell_sort\shell_sort_speed_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF789A86-83A2-4B2E-B396-074AD7273E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113AC97E-9AC0-4443-AA8E-5FB6402A0DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,9 +191,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>SELL</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -288,9 +285,6 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:v>HIBBARD</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -386,15 +380,12 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
-          <c:tx>
-            <c:v>SEDJVIK</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:prstDash val="lgDashDotDot"/>
+              <a:prstDash val="sysDot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -484,9 +475,6 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
-          <c:tx>
-            <c:v>GEOMETRIC</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
